--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,62 +1195,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>186702</v>
+        <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>96313</v>
+        <v>92911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>530</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sunnanvik, sundet S om Näset, Vstm</t>
+          <t>SundetsNstrand2, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547921</v>
+        <v>548148</v>
       </c>
       <c r="R6" t="n">
-        <v>6626060</v>
+        <v>6626126</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,17 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-10-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riklig!</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,73 +1285,61 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Strand med Salix-snår och bäverfällda aspar</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>15 substratenheter # Baserna av Salix-buskar</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/186702</t>
+          <t>https://artportalen.se/Sighting/136801871</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110963181</v>
+        <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92348</v>
+        <v>92911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1367,25 +1347,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>sundetsNstrand3, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548161</v>
+        <v>548166</v>
       </c>
       <c r="R7" t="n">
-        <v>6626153</v>
+        <v>6626123</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,17 +1385,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkroppar.</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,96 +1403,82 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>3 substratenheter # rötter på en gammal, grov tall</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110963181</t>
+          <t>https://artportalen.se/Sighting/136801988</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110962984</v>
+        <v>186702</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>96313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>530</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbron, V, Vstm</t>
+          <t>Sunnanvik, sundet S om Näset, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547753</v>
+        <v>547921</v>
       </c>
       <c r="R8" t="n">
-        <v>6626071</v>
+        <v>6626060</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,12 +1502,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2007-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2007-10-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,47 +1521,46 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>gles blandskog</t>
+          <t>Strand med Salix-snår och bäverfällda aspar</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal, grov tall</t>
+          <t>15 substratenheter # Baserna av Salix-buskar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110962984</t>
+          <t>https://artportalen.se/Sighting/186702</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131650259</v>
+        <v>110963181</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,49 +1568,52 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grevens bro, Vstm</t>
+          <t>Väst Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547915</v>
+        <v>548161</v>
       </c>
       <c r="R9" t="n">
-        <v>6626079</v>
+        <v>6626153</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1673,22 +1637,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkroppar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,83 +1656,100 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>3 substratenheter # rötter på en gammal, grov tall</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131650259</t>
+          <t>https://artportalen.se/Sighting/110963181</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108431226</v>
+        <v>110962984</v>
       </c>
       <c r="B10" t="n">
-        <v>57258</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100065</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Parkering Sundsbron, Vstm</t>
+          <t>Sundsbron, V, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547884</v>
+        <v>547753</v>
       </c>
       <c r="R10" t="n">
-        <v>6626126</v>
+        <v>6626071</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1797,17 +1773,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På åker, stående ca 100 m från parkeringen. Tämligen nära bilvägen. Förmodligen rastande</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,38 +1787,47 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Åker</t>
+          <t>gles blandskog</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal, grov tall</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108431226</t>
+          <t>https://artportalen.se/Sighting/110962984</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108260934</v>
+        <v>131650259</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,27 +1835,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1913,12 +1901,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,7 +1925,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1945,16 +1942,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108260934</t>
+          <t>https://artportalen.se/Sighting/131650259</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110963298</v>
+        <v>108431226</v>
       </c>
       <c r="B12" t="n">
-        <v>101228</v>
+        <v>57258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,53 +1959,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>100065</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>Parkering Sundsbron, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548179</v>
+        <v>547884</v>
       </c>
       <c r="R12" t="n">
-        <v>6626268</v>
+        <v>6626126</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2032,12 +2025,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På åker, stående ca 100 m från parkeringen. Tämligen nära bilvägen. Förmodligen rastande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,39 +2044,38 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>äldre, lundartad lövskog</t>
+          <t>Åker</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110963298</t>
+          <t>https://artportalen.se/Sighting/108431226</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110963336</v>
+        <v>108260934</v>
       </c>
       <c r="B13" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,53 +2083,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>Grevens bro, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548194</v>
+        <v>547915</v>
       </c>
       <c r="R13" t="n">
-        <v>6626327</v>
+        <v>6626079</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2156,12 +2141,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,55 +2159,54 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>äldre, lundartad lövskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110963336</t>
+          <t>https://artportalen.se/Sighting/108260934</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110963540</v>
+        <v>110963298</v>
       </c>
       <c r="B14" t="n">
-        <v>103404</v>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225046</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
@@ -2233,7 +2217,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2242,10 +2230,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548186</v>
+        <v>548179</v>
       </c>
       <c r="R14" t="n">
-        <v>6626367</v>
+        <v>6626268</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2280,11 +2268,6 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett fullvuxet, friskt träd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2313,6 +2296,251 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963298</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110963336</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Väst Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>548194</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6626327</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre, lundartad lövskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963336</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110963540</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Väst Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>548186</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6626367</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett fullvuxet, friskt träd.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre, lundartad lövskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110963540</t>
         </is>
@@ -2333,6 +2561,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,27 +1824,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131650259</v>
+        <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1861,23 +1861,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grevens bro, Vstm</t>
+          <t>strandskogen N Fiskartorpsviken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547915</v>
+        <v>548163</v>
       </c>
       <c r="R11" t="n">
-        <v>6626079</v>
+        <v>6626153</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1901,22 +1901,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ropade</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,27 +1936,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131650259</t>
+          <t>https://artportalen.se/Sighting/136820893</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108431226</v>
+        <v>131650259</v>
       </c>
       <c r="B12" t="n">
-        <v>57258</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,16 +1964,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1978,30 +1983,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Parkering Sundsbron, Vstm</t>
+          <t>Grevens bro, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547884</v>
+        <v>547915</v>
       </c>
       <c r="R12" t="n">
-        <v>6626126</v>
+        <v>6626079</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2025,17 +2030,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På åker, stående ca 100 m från parkeringen. Tämligen nära bilvägen. Förmodligen rastande</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,11 +2056,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Åker</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2066,16 +2071,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108431226</t>
+          <t>https://artportalen.se/Sighting/131650259</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108260934</v>
+        <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>101326</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,41 +2088,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grevens bro, Vstm</t>
+          <t>strandskogen N Fiskartorpsviken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547915</v>
+        <v>548163</v>
       </c>
       <c r="R13" t="n">
-        <v>6626079</v>
+        <v>6626153</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2141,12 +2154,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,34 +2178,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Leif Johansson, Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108260934</t>
+          <t>https://artportalen.se/Sighting/136820939</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110963298</v>
+        <v>108431226</v>
       </c>
       <c r="B14" t="n">
-        <v>101228</v>
+        <v>57258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,53 +2212,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>Parkering Sundsbron, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548179</v>
+        <v>547884</v>
       </c>
       <c r="R14" t="n">
-        <v>6626268</v>
+        <v>6626126</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2260,12 +2278,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På åker, stående ca 100 m från parkeringen. Tämligen nära bilvägen. Förmodligen rastande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,39 +2297,38 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>äldre, lundartad lövskog</t>
+          <t>Åker</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110963298</t>
+          <t>https://artportalen.se/Sighting/108431226</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110963336</v>
+        <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>101228</v>
+        <v>58704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,53 +2336,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>103057</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>strandskogen N Fiskartorpsviken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548194</v>
+        <v>548163</v>
       </c>
       <c r="R15" t="n">
-        <v>6626327</v>
+        <v>6626153</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,12 +2402,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,85 +2426,75 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>äldre, lundartad lövskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110963336</t>
+          <t>https://artportalen.se/Sighting/136820911</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110963540</v>
+        <v>108260934</v>
       </c>
       <c r="B16" t="n">
-        <v>103404</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>225046</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väst Lillsjön, Vstm</t>
+          <t>Grevens bro, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548186</v>
+        <v>547915</v>
       </c>
       <c r="R16" t="n">
-        <v>6626367</v>
+        <v>6626079</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2500,17 +2518,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ett fullvuxet, friskt träd.</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,24 +2536,388 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>äldre, lundartad lövskog</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108260934</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110963298</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Väst Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>548179</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6626268</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>äldre, lundartad lövskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963298</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110963336</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Väst Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>548194</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6626327</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>äldre, lundartad lövskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963336</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110963540</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Väst Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>548186</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6626367</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett fullvuxet, friskt träd.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>äldre, lundartad lövskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110963540</t>
         </is>
@@ -2563,6 +2940,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>136571216</v>
       </c>
       <c r="B5" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>58704</v>
+        <v>58717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>58717</v>
+        <v>58719</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1859,11 +1859,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2112,11 +2108,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2360,11 +2352,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>58719</v>
+        <v>58729</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>58729</v>
+        <v>58731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34243-2026 artfynd.xlsx
+++ b/artfynd/A 34243-2026 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>136801871</v>
       </c>
       <c r="B6" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>136801988</v>
       </c>
       <c r="B7" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136820893</v>
       </c>
       <c r="B11" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136820939</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136820911</v>
       </c>
       <c r="B15" t="n">
-        <v>58731</v>
+        <v>58733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
